--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488249_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488249_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1396</v>
+        <v>2.4646</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9155</v>
+        <v>1.0682</v>
       </c>
       <c r="F2" t="n">
-        <v>1.224</v>
+        <v>1.3964</v>
       </c>
       <c r="G2" t="n">
         <v>1.6723</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8662</v>
+        <v>-0.5413</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.526</v>
+        <v>-0.3734</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3402</v>
+        <v>-0.1679</v>
       </c>
       <c r="V2" t="n">
         <v>1.8894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2685</v>
+        <v>0.9294</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6797</v>
+        <v>1.3652</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4112</v>
+        <v>-0.4359</v>
       </c>
       <c r="G3" t="n">
         <v>1.2388</v>
@@ -688,13 +688,13 @@
         <v>2.594</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8444</v>
+        <v>-1.1835</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4226</v>
+        <v>-0.7371</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4218</v>
+        <v>-0.4465</v>
       </c>
       <c r="V3" t="n">
         <v>0.5034999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3718</v>
+        <v>-1.152</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3736</v>
+        <v>0.0366</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7454</v>
+        <v>-1.1886</v>
       </c>
       <c r="G4" t="n">
         <v>-2.5647</v>
@@ -766,13 +766,13 @@
         <v>2.594</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4223</v>
+        <v>-1.2025</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.4327</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3266</v>
+        <v>-0.7698</v>
       </c>
       <c r="V4" t="n">
         <v>1.133</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8456</v>
+        <v>-1.4057</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3852</v>
+        <v>-1.7393</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4603</v>
+        <v>0.3336</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9011</v>
+        <v>-0.4358</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1468</v>
+        <v>-1.1101</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7543</v>
+        <v>0.6742</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5792</v>
+        <v>0.8488</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0215</v>
+        <v>0.2362</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6007</v>
+        <v>0.6126</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3219</v>
+        <v>-1.2847</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1683</v>
+        <v>-1.3463</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1536</v>
+        <v>0.0616</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3144</v>
+        <v>-1.2886</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3793</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0649</v>
+        <v>-0.7387</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2589</v>
+        <v>0.5041</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>0.5041</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8826</v>
+        <v>-1.5576</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0885</v>
+        <v>-0.9359</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7941</v>
+        <v>-0.6217</v>
       </c>
       <c r="G6" t="n">
         <v>0.3901</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9757</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3071</v>
+        <v>-0.1545</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6685</v>
+        <v>-0.4962</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1345</v>
+        <v>-1.8095</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8807</v>
+        <v>-1.728</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2538</v>
+        <v>-0.0815</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4949</v>
@@ -1000,13 +1000,13 @@
         <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7692</v>
+        <v>-0.4443</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3619</v>
+        <v>-0.2092</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4074</v>
+        <v>-0.235</v>
       </c>
       <c r="V7" t="n">
         <v>0.9444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1494</v>
+        <v>-1.8545</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.987</v>
+        <v>-1.8891</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1624</v>
+        <v>0.0346</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8201</v>
@@ -1078,13 +1078,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4034</v>
+        <v>-0.1085</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0751</v>
+        <v>0.1219</v>
       </c>
       <c r="V8" t="n">
         <v>0.63</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3139</v>
+        <v>-2.0409</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2289</v>
+        <v>-0.679</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-1.3618</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4358</v>
+        <v>-0.9011</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1101</v>
+        <v>-0.1468</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6742</v>
+        <v>-0.7543</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8488</v>
+        <v>-0.5792</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2362</v>
+        <v>0.0215</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6126</v>
+        <v>-0.6007</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2847</v>
+        <v>-0.3219</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3463</v>
+        <v>-0.1683</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0616</v>
+        <v>-0.1536</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.1853</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.0382</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>0.1853</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1968</v>
+        <v>0.1191</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0396</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1572</v>
+        <v>0.0336</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5041</v>
+        <v>-1.2589</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5041</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3887</v>
+        <v>-3.4699</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5916</v>
+        <v>-3.9833</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2028</v>
+        <v>0.5134</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0223</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.723</v>
+        <v>-0.3581</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1716</v>
+        <v>-0.5633</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8946</v>
+        <v>0.2052</v>
       </c>
       <c r="V10" t="n">
         <v>1.7635</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1898</v>
+        <v>-4.1603</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9207</v>
+        <v>-2.768</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2692</v>
+        <v>-1.3923</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7621</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7984</v>
+        <v>-0.7688</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.143</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6554</v>
+        <v>-0.7785</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1421</v>
+        <v>-5.6804</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1668</v>
+        <v>-2.7544</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9753</v>
+        <v>-2.9261</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0357</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1102</v>
+        <v>-0.6485</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8687</v>
+        <v>-0.8195</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6992</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.0103</v>
+        <v>-19.7368</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.2806</v>
+        <v>-14.007</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.7299</v>
+        <v>-5.729900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-12.7355</v>
@@ -1438,7 +1438,7 @@
         <v>-9.894300000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8415</v>
+        <v>-2.841499999999999</v>
       </c>
       <c r="J13" t="n">
         <v>2.1569</v>
@@ -1468,13 +1468,13 @@
         <v>14.823</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.349200000000001</v>
+        <v>-7.0757</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.257900000000001</v>
+        <v>-2.9844</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.091199999999999</v>
+        <v>-4.0914</v>
       </c>
       <c r="V13" t="n">
         <v>3.780399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.4343</v>
+        <v>10.6365</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5015</v>
+        <v>6.8932</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9328</v>
+        <v>3.7433</v>
       </c>
       <c r="G14" t="n">
         <v>9.195499999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3696</v>
+        <v>1.5718</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4514</v>
+        <v>0.8431</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9182</v>
+        <v>0.7287</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3161</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.84</v>
+        <v>9.6287</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4758</v>
+        <v>5.9862</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3642</v>
+        <v>3.6425</v>
       </c>
       <c r="G15" t="n">
         <v>6.0427</v>
@@ -1624,13 +1624,13 @@
         <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1118</v>
+        <v>1.9004</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9213</v>
+        <v>1.4316</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1905</v>
+        <v>0.4688</v>
       </c>
       <c r="V15" t="n">
         <v>0.9444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1471</v>
+        <v>2.9015</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6497</v>
+        <v>1.5518</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4974</v>
+        <v>1.3497</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1837</v>
@@ -1702,13 +1702,13 @@
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0344</v>
+        <v>0.7887</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5609</v>
+        <v>0.4629</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4735</v>
+        <v>0.3258</v>
       </c>
       <c r="V16" t="n">
         <v>0.6289</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6915</v>
+        <v>1.7941</v>
       </c>
       <c r="E17" t="n">
-        <v>0.928</v>
+        <v>-0.6698</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7635</v>
+        <v>2.4639</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0416</v>
+        <v>1.0962</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6852</v>
+        <v>0.0964</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3564</v>
+        <v>0.9998</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4155</v>
+        <v>0.173</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7519</v>
+        <v>-0.4811</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6635</v>
+        <v>0.6541</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3738</v>
+        <v>0.9232</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0667</v>
+        <v>0.5774</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3071</v>
+        <v>0.3457</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4472</v>
+        <v>0.3274</v>
       </c>
       <c r="T17" t="n">
-        <v>0.051</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3962</v>
+        <v>0.2437</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1826</v>
+        <v>1.6423</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1685</v>
+        <v>0.928</v>
       </c>
       <c r="F18" t="n">
-        <v>0.014</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0015</v>
+        <v>2.0416</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5652</v>
+        <v>1.6852</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5638</v>
+        <v>0.3564</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4105</v>
+        <v>2.4155</v>
       </c>
       <c r="K18" t="n">
-        <v>0.369</v>
+        <v>1.7519</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>0.6635</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.412</v>
+        <v>-0.3738</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9343</v>
+        <v>-0.0667</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5223</v>
+        <v>-0.3071</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3706</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.3979</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0555</v>
+        <v>0.3469</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8796</v>
+        <v>0.9312</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3553</v>
+        <v>-0.7638</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2348</v>
+        <v>1.695</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0962</v>
+        <v>1.9645</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0964</v>
+        <v>0.1857</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9998</v>
+        <v>1.7787</v>
       </c>
       <c r="J19" t="n">
-        <v>0.173</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4811</v>
+        <v>0.206</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6541</v>
+        <v>0.7572</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9232</v>
+        <v>1.0013</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5774</v>
+        <v>-0.0203</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3457</v>
+        <v>1.0216</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.9106</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6019</v>
+        <v>0.1259</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0147</v>
+        <v>0.7847</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6546</v>
+        <v>0.8899</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0576</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7121</v>
+        <v>0.211</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9645</v>
+        <v>-0.0015</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1857</v>
+        <v>-0.5652</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7787</v>
+        <v>0.5638</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.4105</v>
       </c>
       <c r="K20" t="n">
-        <v>0.206</v>
+        <v>0.369</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7572</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0013</v>
+        <v>-0.412</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0203</v>
+        <v>-0.9343</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0216</v>
+        <v>0.5223</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6339</v>
+        <v>0.5214</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1679</v>
+        <v>0.2689</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8018</v>
+        <v>0.2524</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5733</v>
+        <v>-0.0005</v>
       </c>
       <c r="W20" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.5733</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0915</v>
+        <v>-0.5972</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5059</v>
+        <v>-1.1914</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4144</v>
+        <v>0.5942</v>
       </c>
       <c r="G21" t="n">
         <v>0.6993</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>0.728</v>
+        <v>0.2223</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8133</v>
+        <v>0.1278</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0853</v>
+        <v>0.0945</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8894</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8152</v>
+        <v>-1.1778</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6599</v>
+        <v>-0.1702</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1553</v>
+        <v>-1.0076</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3463</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5245</v>
+        <v>0.1129</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3619</v>
+        <v>0.1278</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1627</v>
+        <v>-0.0149</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9444</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.725</v>
+        <v>-2.5292</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2482</v>
+        <v>-3.0524</v>
       </c>
       <c r="F23" t="n">
         <v>0.5232</v>
@@ -2248,10 +2248,10 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>0.48</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.092</v>
+        <v>0.1039</v>
       </c>
       <c r="U23" t="n">
         <v>0.572</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1877</v>
+        <v>-3.4568</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1668</v>
+        <v>-4.4606</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9792</v>
+        <v>1.0038</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0298</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8421</v>
+        <v>0.573</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.4648</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1082</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>20.0103</v>
+        <v>20.6632</v>
       </c>
       <c r="E25" t="n">
-        <v>5.729799999999999</v>
+        <v>5.7299</v>
       </c>
       <c r="F25" t="n">
-        <v>14.2803</v>
+        <v>14.9332</v>
       </c>
       <c r="G25" t="n">
         <v>12.7356</v>
@@ -2383,7 +2383,7 @@
         <v>14.2027</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6899000000000011</v>
+        <v>0.6899000000000002</v>
       </c>
       <c r="M25" t="n">
         <v>-2.1569</v>
@@ -2404,16 +2404,16 @@
         <v>18.5287</v>
       </c>
       <c r="S25" t="n">
-        <v>7.349300000000001</v>
+        <v>8.0023</v>
       </c>
       <c r="T25" t="n">
-        <v>4.0914</v>
+        <v>4.0913</v>
       </c>
       <c r="U25" t="n">
-        <v>3.258</v>
+        <v>3.9108</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.7804</v>
+        <v>-3.780399999999999</v>
       </c>
       <c r="W25" t="n">
         <v>1.5688</v>
